--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_369_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_369_R37.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8241</v>
+        <v>0.7768</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6586</v>
+        <v>0.208</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1655</v>
+        <v>0.5688</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.0564</v>
+        <v>1.4928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9014</v>
+        <v>1.2819</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.9578</v>
+        <v>0.2109</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3694</v>
+        <v>2.3188</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1665</v>
+        <v>2.2084</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.5359</v>
+        <v>0.1104</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.687</v>
+        <v>-0.826</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2651</v>
+        <v>-0.9265</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.422</v>
+        <v>0.1005</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8109</v>
+        <v>0.284</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1181</v>
+        <v>0.2087</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6928</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5949</v>
+        <v>0.6852</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3875</v>
+        <v>0.8893</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2074</v>
+        <v>-0.2042</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4928</v>
+        <v>-2.0564</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2819</v>
+        <v>0.9014</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2109</v>
+        <v>-2.9578</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3188</v>
+        <v>-0.3694</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2084</v>
+        <v>1.1665</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>-1.5359</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.826</v>
+        <v>-1.687</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9265</v>
+        <v>-0.2651</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1005</v>
+        <v>-1.422</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1021</v>
+        <v>1.672</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3882</v>
+        <v>1.3489</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7139</v>
+        <v>0.3231</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>S. MILTON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4107</v>
+        <v>0.6594</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5074</v>
+        <v>1.6055</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.946</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7468</v>
+        <v>-2.2256</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2917</v>
+        <v>-2.0182</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4551</v>
+        <v>-0.2074</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3932</v>
+        <v>-0.1593</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3564</v>
+        <v>-0.5875</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>0.4282</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3536</v>
+        <v>-2.0663</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.4306</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4183</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5764</v>
+        <v>0.2045</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3462</v>
+        <v>0.476</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2302</v>
+        <v>-0.2715</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6083</v>
+        <v>2.6805</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MILTON</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0977</v>
+        <v>0.3435</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2516</v>
+        <v>0.5074</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3493</v>
+        <v>-0.1639</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2256</v>
+        <v>0.7468</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0182</v>
+        <v>0.2917</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2074</v>
+        <v>0.4551</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1593</v>
+        <v>0.3932</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5875</v>
+        <v>0.3564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4282</v>
+        <v>0.0368</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0663</v>
+        <v>0.3536</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4306</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.4183</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5526</v>
+        <v>0.5091</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1221</v>
+        <v>0.3462</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6748</v>
+        <v>0.163</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6805</v>
+        <v>-1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9623</v>
+        <v>-0.6427</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8094</v>
+        <v>0.9274</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7717</v>
+        <v>-1.5701</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7238</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4551</v>
+        <v>-0.1355</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3778</v>
+        <v>0.4957</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8329</v>
+        <v>-0.6313</v>
       </c>
       <c r="V7" t="n">
         <v>2.1444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9593</v>
+        <v>-1.0322</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.081</v>
+        <v>-1.0195</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1217</v>
+        <v>-0.0127</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9441</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5693</v>
+        <v>0.3578</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8883</v>
+        <v>0.1733</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3189</v>
+        <v>0.1845</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0259</v>
+        <v>-1.141</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1753</v>
+        <v>0.8944</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8506</v>
+        <v>-2.0354</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4943</v>
+        <v>-2.2415</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4103</v>
+        <v>-0.448</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0841</v>
+        <v>-1.7935</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5111</v>
+        <v>-0.6044</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2017</v>
+        <v>0.1855</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7127</v>
+        <v>-0.7899</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9833</v>
+        <v>-1.6372</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.612</v>
+        <v>-0.6335</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3713</v>
+        <v>-1.0037</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2274</v>
+        <v>-0.8452</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6642</v>
+        <v>-0.2513</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5632</v>
+        <v>-0.5939</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3535</v>
+        <v>-1.5376</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0492</v>
+        <v>-0.8214</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3043</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2415</v>
+        <v>-1.4943</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.448</v>
+        <v>-0.4103</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7935</v>
+        <v>-1.0841</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6044</v>
+        <v>-0.5111</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1855</v>
+        <v>0.2017</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7899</v>
+        <v>-0.7127</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6372</v>
+        <v>-0.9833</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6335</v>
+        <v>-0.612</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0037</v>
+        <v>-0.3713</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0577</v>
+        <v>-0.7391</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1949</v>
+        <v>-0.3104</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8628</v>
+        <v>-0.4288</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7483</v>
+        <v>-4.4287</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5695</v>
+        <v>-4.4516</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1788</v>
+        <v>0.0228</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9866</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5298</v>
+        <v>-0.2102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1098</v>
+        <v>0.0081</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.42</v>
+        <v>-0.2183</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1348,10 +1348,10 @@
         <v>-6.928100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3352</v>
+        <v>-1.335200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.592899999999999</v>
+        <v>-5.593000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-13.8115</v>
@@ -1375,10 +1375,10 @@
         <v>-11.4574</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.117599999999999</v>
+        <v>-5.1176</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.3398</v>
+        <v>-6.339799999999999</v>
       </c>
       <c r="P12" t="n">
         <v>3.4794</v>
@@ -1390,10 +1390,10 @@
         <v>11.5977</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8654999999999997</v>
+        <v>0.8654000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>2.420500000000001</v>
+        <v>2.4205</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5552</v>
@@ -1405,7 +1405,7 @@
         <v>6.716799999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.1781</v>
+        <v>-4.178100000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7939</v>
+        <v>7.0628</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8009</v>
+        <v>6.7445</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.007</v>
+        <v>0.3183</v>
       </c>
       <c r="G13" t="n">
         <v>4.0915</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2797</v>
+        <v>-0.0108</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8215</v>
+        <v>0.1221</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4582</v>
+        <v>-0.1329</v>
       </c>
       <c r="V13" t="n">
         <v>2.2862</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4345</v>
+        <v>3.6761</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7387</v>
+        <v>3.8566</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3041</v>
+        <v>-0.1805</v>
       </c>
       <c r="G14" t="n">
         <v>5.0707</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8834</v>
+        <v>-0.6418</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0351</v>
+        <v>0.0828</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.7246</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1444</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4014</v>
+        <v>1.1413</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2799</v>
+        <v>-0.2596</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6812</v>
+        <v>1.4008</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7152</v>
+        <v>1.3872</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4369</v>
+        <v>-0.2254</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2783</v>
+        <v>1.6126</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9581</v>
+        <v>0.3978</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1484</v>
+        <v>-0.8501</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8097</v>
+        <v>1.2479</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7571</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2885</v>
+        <v>0.6246</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4685</v>
+        <v>0.3648</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5515</v>
+        <v>-1.8556</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0779</v>
+        <v>-0.3903</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3135</v>
+        <v>0.1261</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7644</v>
+        <v>-0.5164</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0734</v>
+        <v>0.8268</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4955</v>
+        <v>0.2856</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5689</v>
+        <v>0.5412</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3872</v>
+        <v>2.1354</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2254</v>
+        <v>1.9915</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6126</v>
+        <v>0.1438</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3978</v>
+        <v>1.5248</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8501</v>
+        <v>1.2204</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2479</v>
+        <v>0.3044</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.6106</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6246</v>
+        <v>0.7711</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3648</v>
+        <v>-0.1605</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.8556</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4582</v>
+        <v>-0.7029</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1098</v>
+        <v>-0.4558</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3484</v>
+        <v>-0.2471</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
         <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0597</v>
+        <v>0.7577</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7949000000000001</v>
+        <v>-1.3414</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2648</v>
+        <v>2.0992</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9991</v>
+        <v>1.7152</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1826</v>
+        <v>0.4369</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8165</v>
+        <v>1.2783</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.023</v>
+        <v>0.9581</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6855</v>
+        <v>0.1484</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6625</v>
+        <v>0.8097</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0222</v>
+        <v>0.7571</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8681</v>
+        <v>0.2885</v>
       </c>
       <c r="O17" t="n">
-        <v>0.154</v>
+        <v>0.4685</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0606</v>
+        <v>0.4343</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0499</v>
+        <v>0.2519</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9893</v>
+        <v>0.1823</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.577</v>
+        <v>0.6374</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3309</v>
+        <v>-0.0307</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9079</v>
+        <v>0.6681</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3007</v>
+        <v>0.9991</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3542</v>
+        <v>0.1826</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0535</v>
+        <v>0.8165</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0504</v>
+        <v>-0.023</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0504</v>
+        <v>-0.6855</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6625</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2502</v>
+        <v>1.0222</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3038</v>
+        <v>0.8681</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0535</v>
+        <v>0.154</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0444</v>
+        <v>-0.3618</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1494</v>
+        <v>0.2243</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1937</v>
+        <v>-0.586</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3379</v>
+        <v>0.5434</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3042</v>
+        <v>-0.3309</v>
       </c>
       <c r="F19" t="n">
-        <v>0.642</v>
+        <v>0.8743</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1354</v>
+        <v>0.3007</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9915</v>
+        <v>0.3542</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1438</v>
+        <v>-0.0535</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5248</v>
+        <v>0.0504</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2204</v>
+        <v>0.0504</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3044</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6106</v>
+        <v>0.2502</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7711</v>
+        <v>0.3038</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1605</v>
+        <v>-0.0535</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1918</v>
+        <v>0.0108</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0455</v>
+        <v>-0.1494</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1463</v>
+        <v>0.1601</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5806</v>
+        <v>-0.3618</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5455</v>
+        <v>1.6635</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1261</v>
+        <v>-2.0253</v>
       </c>
       <c r="G20" t="n">
         <v>1.4912</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6963</v>
+        <v>0.9151</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4129</v>
+        <v>0.5309</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2834</v>
+        <v>0.3842</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7434</v>
+        <v>-1.2551</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5496</v>
+        <v>-1.1957</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1938</v>
+        <v>-0.0593</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1346</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.1926</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4328</v>
+        <v>-2.209</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.025</v>
+        <v>-1.2609</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4078</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9625</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0499</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4274</v>
+        <v>0.0323</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3247</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9929</v>
+        <v>-3.1052</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.23</v>
+        <v>-1.4659</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7629</v>
+        <v>-1.6393</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2822</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0.127</v>
+        <v>0.0147</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1889</v>
+        <v>-0.047</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0619</v>
+        <v>0.0617</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6778999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.928100000000001</v>
+        <v>7.714400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>6.664899999999999</v>
+        <v>6.665100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2630999999999994</v>
+        <v>1.0494</v>
       </c>
       <c r="G24" t="n">
         <v>13.8117</v>
@@ -2326,13 +2326,13 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8652999999999997</v>
+        <v>-0.07899999999999989</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5551</v>
+        <v>1.555</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.4205</v>
+        <v>-1.6342</v>
       </c>
       <c r="V24" t="n">
         <v>-2.5387</v>
